--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>253</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>332</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>316</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>219</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>258</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>358</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>349</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>258</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>295</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>363</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>285</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>338</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>322</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>260</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>353</v>
+        <v>371</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>284</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>205</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>367</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>268</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>255</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>260</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>172</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>243</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>237</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>354</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>257</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>274</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>265</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>259</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>153</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>365</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>248</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>338</v>
+        <v>329</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>329</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>318</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>232</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>306</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>257</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>272</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>356</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>267</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>357</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>246</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>306</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>305</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>282</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>316</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>384</v>
+        <v>364</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>295</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>364</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>265</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>301</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>386</v>
+        <v>371</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>288</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>371</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>280</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>421</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>331</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>440</v>
+        <v>453</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>439</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>334</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>316</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>180</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>403</v>
+        <v>380</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>297</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>167</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>380</v>
+        <v>364</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>281</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>158</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>244</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>271</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>372</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>269</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>340</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/output/japan.xlsx
+++ b/output/japan.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
